--- a/Hydraulics/pipeline_input_noiso.xlsx
+++ b/Hydraulics/pipeline_input_noiso.xlsx
@@ -10,9 +10,10 @@
     <sheet name="Pipeline_Input" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="_FittingList" sheetId="2" state="hidden" r:id="rId2"/>
     <sheet name="Notes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="UNITS" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pipeline_Input'!$A$2:$AH$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pipeline_Input'!$A$2:$AK$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +59,30 @@
       <color rgb="00404040"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -79,6 +102,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -108,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -124,6 +152,30 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -489,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH12"/>
+  <dimension ref="A1:AK20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -525,13 +577,16 @@
     <col width="10" customWidth="1" min="31" max="31"/>
     <col width="12" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="30" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="14" customWidth="1" min="35" max="35"/>
+    <col width="16" customWidth="1" min="36" max="36"/>
+    <col width="30" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NO-ISO PIPELINE INPUT  —  Group rows into hydraulic circuits using column A (Circuit).  All rows with the same Circuit ID are processed in series → one workbook per circuit.</t>
+          <t>NO-ISO PIPELINE INPUT  —  Group rows into hydraulic circuits using column A (Circuit).  All rows with the same Circuit ID are processed in series → one workbook per circuit.  Units: FPS (see UNITS sheet).</t>
         </is>
       </c>
     </row>
@@ -593,12 +648,12 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Temp (degF)</t>
+          <t>Temp (°F)</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Vapor Mass Flow</t>
+          <t>Vapor Mass Flow (lb/hr)</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -628,7 +683,7 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>Liq Mass Flow (lb/h)</t>
+          <t>Liq Mass Flow (lb/hr)</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
@@ -702,6 +757,21 @@
         </is>
       </c>
       <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>Set P (psia)</t>
+        </is>
+      </c>
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>Control Valve Type</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>Exch Max Allow dP (psi)</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -779,7 +849,10 @@
       <c r="AE3" s="3" t="n"/>
       <c r="AF3" s="3" t="n"/>
       <c r="AG3" s="3" t="n"/>
-      <c r="AH3" s="3" t="inlineStr">
+      <c r="AH3" s="3" t="n"/>
+      <c r="AI3" s="3" t="n"/>
+      <c r="AJ3" s="3" t="n"/>
+      <c r="AK3" s="3" t="inlineStr">
         <is>
           <t>Entrance</t>
         </is>
@@ -855,7 +928,10 @@
       <c r="AE4" s="3" t="n"/>
       <c r="AF4" s="3" t="n"/>
       <c r="AG4" s="3" t="n"/>
-      <c r="AH4" s="3" t="inlineStr">
+      <c r="AH4" s="3" t="n"/>
+      <c r="AI4" s="3" t="n"/>
+      <c r="AJ4" s="3" t="n"/>
+      <c r="AK4" s="3" t="inlineStr">
         <is>
           <t>Drop leg</t>
         </is>
@@ -928,6 +1004,9 @@
       <c r="AF5" s="3" t="n"/>
       <c r="AG5" s="3" t="n"/>
       <c r="AH5" s="3" t="n"/>
+      <c r="AI5" s="3" t="n"/>
+      <c r="AJ5" s="3" t="n"/>
+      <c r="AK5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -997,7 +1076,10 @@
       <c r="AE6" s="3" t="n"/>
       <c r="AF6" s="3" t="n"/>
       <c r="AG6" s="3" t="n"/>
-      <c r="AH6" s="3" t="inlineStr">
+      <c r="AH6" s="3" t="n"/>
+      <c r="AI6" s="3" t="n"/>
+      <c r="AJ6" s="3" t="n"/>
+      <c r="AK6" s="3" t="inlineStr">
         <is>
           <t>40% splits to branch</t>
         </is>
@@ -1071,7 +1153,10 @@
       <c r="AE7" s="3" t="n"/>
       <c r="AF7" s="3" t="n"/>
       <c r="AG7" s="3" t="n"/>
-      <c r="AH7" s="3" t="inlineStr">
+      <c r="AH7" s="3" t="n"/>
+      <c r="AI7" s="3" t="n"/>
+      <c r="AJ7" s="3" t="n"/>
+      <c r="AK7" s="3" t="inlineStr">
         <is>
           <t>PSV seat loss</t>
         </is>
@@ -1143,7 +1228,10 @@
       <c r="AE8" s="3" t="n"/>
       <c r="AF8" s="3" t="n"/>
       <c r="AG8" s="3" t="n"/>
-      <c r="AH8" s="3" t="inlineStr">
+      <c r="AH8" s="3" t="n"/>
+      <c r="AI8" s="3" t="n"/>
+      <c r="AJ8" s="3" t="n"/>
+      <c r="AK8" s="3" t="inlineStr">
         <is>
           <t>Header run</t>
         </is>
@@ -1216,6 +1304,9 @@
       <c r="AF9" s="3" t="n"/>
       <c r="AG9" s="3" t="n"/>
       <c r="AH9" s="3" t="n"/>
+      <c r="AI9" s="3" t="n"/>
+      <c r="AJ9" s="3" t="n"/>
+      <c r="AK9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1285,7 +1376,10 @@
       <c r="AE10" s="3" t="n"/>
       <c r="AF10" s="3" t="n"/>
       <c r="AG10" s="3" t="n"/>
-      <c r="AH10" s="3" t="inlineStr">
+      <c r="AH10" s="3" t="n"/>
+      <c r="AI10" s="3" t="n"/>
+      <c r="AJ10" s="3" t="n"/>
+      <c r="AK10" s="3" t="inlineStr">
         <is>
           <t>CV K=7.2</t>
         </is>
@@ -1373,7 +1467,10 @@
       <c r="AE11" s="3" t="n"/>
       <c r="AF11" s="3" t="n"/>
       <c r="AG11" s="3" t="n"/>
-      <c r="AH11" s="3" t="inlineStr">
+      <c r="AH11" s="3" t="n"/>
+      <c r="AI11" s="3" t="n"/>
+      <c r="AJ11" s="3" t="n"/>
+      <c r="AK11" s="3" t="inlineStr">
         <is>
           <t>Manual props (no stream)</t>
         </is>
@@ -1446,18 +1543,658 @@
       <c r="AF12" s="3" t="n"/>
       <c r="AG12" s="3" t="n"/>
       <c r="AH12" s="3" t="n"/>
+      <c r="AI12" s="3" t="n"/>
+      <c r="AJ12" s="3" t="n"/>
+      <c r="AK12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>L-301</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>T801-OH</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
+      <c r="Q13" s="4" t="n"/>
+      <c r="R13" s="4" t="n"/>
+      <c r="S13" s="4" t="n"/>
+      <c r="T13" s="4" t="n"/>
+      <c r="U13" s="4" t="n"/>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>SRC-01</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>G1A-5</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="3" t="n"/>
+      <c r="AC13" s="3" t="n"/>
+      <c r="AD13" s="3" t="n"/>
+      <c r="AE13" s="3" t="n"/>
+      <c r="AF13" s="3" t="n"/>
+      <c r="AG13" s="3" t="n"/>
+      <c r="AH13" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AI13" s="3" t="n"/>
+      <c r="AJ13" s="3" t="n"/>
+      <c r="AK13" s="3" t="inlineStr">
+        <is>
+          <t>Upstream source pressure</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>L-301</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
+      <c r="Q14" s="4" t="n"/>
+      <c r="R14" s="4" t="n"/>
+      <c r="S14" s="4" t="n"/>
+      <c r="T14" s="4" t="n"/>
+      <c r="U14" s="4" t="n"/>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>P-301</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>Straight Pipeline</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>G1A-5</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3" t="n"/>
+      <c r="AC14" s="3" t="n"/>
+      <c r="AD14" s="3" t="n"/>
+      <c r="AE14" s="3" t="n"/>
+      <c r="AF14" s="3" t="n"/>
+      <c r="AG14" s="3" t="n"/>
+      <c r="AH14" s="3" t="n"/>
+      <c r="AI14" s="3" t="n"/>
+      <c r="AJ14" s="3" t="n"/>
+      <c r="AK14" s="3" t="inlineStr">
+        <is>
+          <t>Run to valve</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>L-301</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="n"/>
+      <c r="P15" s="4" t="n"/>
+      <c r="Q15" s="4" t="n"/>
+      <c r="R15" s="4" t="n"/>
+      <c r="S15" s="4" t="n"/>
+      <c r="T15" s="4" t="n"/>
+      <c r="U15" s="4" t="n"/>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>FCV-301</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>Control Valve</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>G1A-5</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="3" t="n"/>
+      <c r="AC15" s="3" t="n"/>
+      <c r="AD15" s="3" t="n"/>
+      <c r="AE15" s="3" t="n"/>
+      <c r="AF15" s="3" t="n"/>
+      <c r="AG15" s="3" t="n"/>
+      <c r="AH15" s="3" t="n"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="n"/>
+      <c r="AK15" s="3" t="inlineStr">
+        <is>
+          <t>Flow control — ΔP floats to Destination P</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>L-301</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="4" t="n"/>
+      <c r="O16" s="4" t="n"/>
+      <c r="P16" s="4" t="n"/>
+      <c r="Q16" s="4" t="n"/>
+      <c r="R16" s="4" t="n"/>
+      <c r="S16" s="4" t="n"/>
+      <c r="T16" s="4" t="n"/>
+      <c r="U16" s="4" t="n"/>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>DST-01</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>G1A-5</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="3" t="n"/>
+      <c r="AC16" s="3" t="n"/>
+      <c r="AD16" s="3" t="n"/>
+      <c r="AE16" s="3" t="n"/>
+      <c r="AF16" s="3" t="n"/>
+      <c r="AG16" s="3" t="n"/>
+      <c r="AH16" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI16" s="3" t="n"/>
+      <c r="AJ16" s="3" t="n"/>
+      <c r="AK16" s="3" t="inlineStr">
+        <is>
+          <t>Downstream destination pressure</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>L-401</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>T801-OH</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n"/>
+      <c r="P17" s="4" t="n"/>
+      <c r="Q17" s="4" t="n"/>
+      <c r="R17" s="4" t="n"/>
+      <c r="S17" s="4" t="n"/>
+      <c r="T17" s="4" t="n"/>
+      <c r="U17" s="4" t="n"/>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>SRC-02</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>G1A-5</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="3" t="n"/>
+      <c r="AC17" s="3" t="n"/>
+      <c r="AD17" s="3" t="n"/>
+      <c r="AE17" s="3" t="n"/>
+      <c r="AF17" s="3" t="n"/>
+      <c r="AG17" s="3" t="n"/>
+      <c r="AH17" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="AI17" s="3" t="n"/>
+      <c r="AJ17" s="3" t="n"/>
+      <c r="AK17" s="3" t="inlineStr">
+        <is>
+          <t>Header source</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>L-401</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="J18" s="3" t="n"/>
+      <c r="K18" s="3" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
+      <c r="Q18" s="4" t="n"/>
+      <c r="R18" s="4" t="n"/>
+      <c r="S18" s="4" t="n"/>
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="4" t="n"/>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>TEE-40</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>Tee Split Branch Flow 1</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>G1A-5</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="3" t="n"/>
+      <c r="AC18" s="3" t="n"/>
+      <c r="AD18" s="3" t="n"/>
+      <c r="AE18" s="3" t="n"/>
+      <c r="AF18" s="3" t="n"/>
+      <c r="AG18" s="3" t="n"/>
+      <c r="AH18" s="3" t="n"/>
+      <c r="AI18" s="3" t="n"/>
+      <c r="AJ18" s="3" t="n"/>
+      <c r="AK18" s="3" t="inlineStr">
+        <is>
+          <t>50% splits to parallel branch</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>L-401</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
+      <c r="Q19" s="4" t="n"/>
+      <c r="R19" s="4" t="n"/>
+      <c r="S19" s="4" t="n"/>
+      <c r="T19" s="4" t="n"/>
+      <c r="U19" s="4" t="n"/>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>FCV-40A</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>Control Valve</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>G1A-5</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="3" t="n"/>
+      <c r="AC19" s="3" t="n"/>
+      <c r="AD19" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE19" s="3" t="n"/>
+      <c r="AF19" s="3" t="n"/>
+      <c r="AG19" s="3" t="n"/>
+      <c r="AH19" s="3" t="n"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="n"/>
+      <c r="AK19" s="3" t="inlineStr">
+        <is>
+          <t>Main-leg valve (50% flow)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>L-401</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n"/>
+      <c r="O20" s="4" t="n"/>
+      <c r="P20" s="4" t="n"/>
+      <c r="Q20" s="4" t="n"/>
+      <c r="R20" s="4" t="n"/>
+      <c r="S20" s="4" t="n"/>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="4" t="n"/>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>FCV-40B</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>Control Valve</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>G1A-5</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3" t="n"/>
+      <c r="AC20" s="3" t="n"/>
+      <c r="AD20" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE20" s="3" t="n"/>
+      <c r="AF20" s="3" t="n"/>
+      <c r="AG20" s="3" t="n"/>
+      <c r="AH20" s="3" t="n"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="n"/>
+      <c r="AK20" s="3" t="inlineStr">
+        <is>
+          <t>Parallel-leg valve (other 50% flow)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AH2"/>
+  <autoFilter ref="A2:AK2"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:AH1"/>
+    <mergeCell ref="A1:AK1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="F3:F2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Main,Branch"</formula1>
     </dataValidation>
+    <dataValidation sqref="AI3:AI2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Control Valve Type" error="F=flow, P=pressure, T=temperature, L=level control" type="list">
+      <formula1>"F,P,T,L"</formula1>
+    </dataValidation>
     <dataValidation sqref="W3:W2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Fitting" error="Choose a fitting from the list" type="list">
-      <formula1>_FittingList!$A$1:$A$55</formula1>
+      <formula1>_FittingList!$A$1:$A$58</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1470,7 +2207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A55"/>
+  <dimension ref="A1:A58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1855,6 +2592,27 @@
       <c r="A55" t="inlineStr">
         <is>
           <t>Venturi</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Control Valve</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Destination</t>
         </is>
       </c>
     </row>
@@ -1869,7 +2627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A43"/>
+  <dimension ref="A1:A64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -2118,25 +2876,566 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>BRANCHES</t>
+          <t>SOURCE / DESTINATION  (boundary fittings)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Set Run Type = Branch.  Fill Start P on the first Branch row.</t>
+          <t xml:space="preserve">  Source: enter the upstream pressure in 'Set P (psia)' — it anchors the circuit inlet pressure.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Destination: enter the downstream pressure in 'Set P (psia)' — the target the circuit must reach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  If BOTH are filled, a Control Valve placed between them absorbs the pressure difference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  If only one is filled, the pressure is taken from that single value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>CONTROL VALVE  (Fitting = 'Control Valve')</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Set 'Control Valve Type' = F (flow), P (pressure), T (temperature) or L (level).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  F (flow): ΔP floats so the running pressure lands on the downstream Destination 'Set P'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  P / L: fixed design ΔP — enter it in 'Fixed dP (psi)' (or a resistance in 'Fixed K').</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  T (temperature): like a fixed ΔP, but floored at 'Exch Max Allow dP (psi)' (exchanger limit).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  β ratio = valve Bore (in) ÷ upstream line bore is reported in the Notes column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SERIES valves: place several Control Valve rows in Seq order on the same run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PARALLEL valves: split flow at a Tee (negative 'Flow Fraction from Main'), put one Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Valve on the Main leg and one on a Branch (Run Type = Branch, with its own Start P).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>BRANCHES</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Set Run Type = Branch.  Fill Start P on the first Branch row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Branches are marched independently.  FIV/AIV/regime sheets use the Main run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>UNITS</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  This workbook is in FPS units (see the UNITS sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Change the Unit System cell (or per-quantity overrides) on the UNITS sheet and enter values accordingly —</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  the engine reads the UNITS sheet and presents all results in the same units.  Bore/NPS is ALWAYS inches.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C00000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>UNITS  —  choose FPS or SI; per-quantity overrides optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Unit System</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>FPS</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>← FPS or SI.  All inputs read &amp; all results written in these units.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Qty code</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Unit override (optional)</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Options</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Pressure (absolute)</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>default: psia   |   psia | psig | kPa | kPag | MPa | bara | barg | kg/cm2a | kg/cm2g</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>dP</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Pressure drop</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>default: psi   |   psi | kPa | bar | mbar | kg/cm2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Temperature</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>default: degF   |   degF | °F | degC | °C | K</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>dT</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Temperature difference</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>default: degF   |   degF | degC | K</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>mflow</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Mass flow</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>default: lb/hr   |   lb/hr | lb/h | kg/hr | kg/h | kg/s | t/h</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>molflow</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Molar flow</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>default: lb-mol/hr   |   lb-mol/hr | kgmol/hr | kmol/h</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>rho</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Density</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>default: lb/ft3   |   lb/ft3 | lb/ft³ | kg/m3 | kg/m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Length / elevation</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>default: ft   |   ft | m | mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Lin</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Bore / small length</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>default: in   |   in | mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Surface area</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>default: ft2   |   ft2 | ft² | m2 | m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Ain</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Orifice area</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>default: in2   |   in2 | in² | cm2 | cm² | mm2 | mm²</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>default: ft3   |   ft3 | ft³ | m3 | m³ | L</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Heat duty</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>default: BTU/hr   |   BTU/hr | kW | W | MW | MMBTU/hr | kcal/h</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Specific enthalpy / latent heat</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>default: BTU/lb   |   BTU/lb | kJ/kg | kcal/kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>default: ft/s   |   ft/s | m/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>qvol</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Volumetric flow</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>default: ft3/hr   |   ft3/hr | m3/h | gpm | m3/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>visc</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Viscosity</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>default: cP   |   cP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Molecular weight</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>default: g/mol   |   g/mol</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>Leave overrides blank to use the system defaults. Overrides apply per quantity (e.g. P = barg while system = SI).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"FPS,SI"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Hydraulics/pipeline_input_noiso.xlsx
+++ b/Hydraulics/pipeline_input_noiso.xlsx
@@ -13,7 +13,7 @@
     <sheet name="UNITS" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pipeline_Input'!$A$2:$AK$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pipeline_Input'!$A$2:$AU$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK20"/>
+  <dimension ref="A1:AU20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -553,34 +553,44 @@
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="32" customWidth="1" min="23" max="23"/>
-    <col width="9" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
-    <col width="13" customWidth="1" min="27" max="27"/>
-    <col width="10" customWidth="1" min="28" max="28"/>
-    <col width="9" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="10" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="32" customWidth="1" min="25" max="25"/>
+    <col width="9" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="9" customWidth="1" min="31" max="31"/>
     <col width="12" customWidth="1" min="32" max="32"/>
-    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="10" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="16" customWidth="1" min="36" max="36"/>
-    <col width="30" customWidth="1" min="37" max="37"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="14" customWidth="1" min="37" max="37"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="15" customWidth="1" min="39" max="39"/>
+    <col width="16" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="10" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
+    <col width="12" customWidth="1" min="44" max="44"/>
+    <col width="13" customWidth="1" min="45" max="45"/>
+    <col width="15" customWidth="1" min="46" max="46"/>
+    <col width="30" customWidth="1" min="47" max="47"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -633,145 +643,195 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>Upstream Line No</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Upstream Seq</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
           <t>Flow Fraction from Main</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Mass Vapor Fraction Carry Over</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Mass Liquid Fraction Carry Over</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Temp (°F)</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Vapor Mass Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Vap MW</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>Vap Visc (cP)</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>Vap Z</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Vap Cp/Cv</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>Vap Density (lb/ft3)</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>Liq Mass Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>Liq Density (lb/ft3)</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>Liq Visc (cP)</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>Comp ID</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>Fitting Name</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>Bore (in)</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>Piping Spec</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>Length (ft)</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>Elev Change (ft)</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AD2" s="2" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="AC2" s="2" t="inlineStr">
+      <c r="AE2" s="2" t="inlineStr">
         <is>
           <t>Fixed K</t>
         </is>
       </c>
-      <c r="AD2" s="2" t="inlineStr">
+      <c r="AF2" s="2" t="inlineStr">
         <is>
           <t>Fixed dP (psi)</t>
         </is>
       </c>
-      <c r="AE2" s="2" t="inlineStr">
+      <c r="AG2" s="2" t="inlineStr">
         <is>
           <t>Instr Type</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr">
+      <c r="AH2" s="2" t="inlineStr">
         <is>
           <t>Instr Tag</t>
         </is>
       </c>
-      <c r="AG2" s="2" t="inlineStr">
+      <c r="AI2" s="2" t="inlineStr">
         <is>
           <t>Instr dP (psi)</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="inlineStr">
+      <c r="AJ2" s="2" t="inlineStr">
         <is>
           <t>Set P (psia)</t>
         </is>
       </c>
-      <c r="AI2" s="2" t="inlineStr">
+      <c r="AK2" s="2" t="inlineStr">
         <is>
           <t>Control Valve Type</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr">
+      <c r="AL2" s="2" t="inlineStr">
         <is>
           <t>Exch Max Allow dP (psi)</t>
         </is>
       </c>
-      <c r="AK2" s="2" t="inlineStr">
+      <c r="AM2" s="2" t="inlineStr">
+        <is>
+          <t>Valve Body Style</t>
+        </is>
+      </c>
+      <c r="AN2" s="2" t="inlineStr">
+        <is>
+          <t>Valve Characteristic</t>
+        </is>
+      </c>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>Design Opening %</t>
+        </is>
+      </c>
+      <c r="AP2" s="2" t="inlineStr">
+        <is>
+          <t>Rated Cv</t>
+        </is>
+      </c>
+      <c r="AQ2" s="2" t="inlineStr">
+        <is>
+          <t>Min Flow Mult</t>
+        </is>
+      </c>
+      <c r="AR2" s="2" t="inlineStr">
+        <is>
+          <t>Max Flow Mult</t>
+        </is>
+      </c>
+      <c r="AS2" s="2" t="inlineStr">
+        <is>
+          <t>Noise Limit dBA</t>
+        </is>
+      </c>
+      <c r="AT2" s="2" t="inlineStr">
+        <is>
+          <t>Seat Leakage Class</t>
+        </is>
+      </c>
+      <c r="AU2" s="2" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -809,8 +869,8 @@
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
-      <c r="L3" s="4" t="n"/>
-      <c r="M3" s="4" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
       <c r="N3" s="4" t="n"/>
       <c r="O3" s="4" t="n"/>
       <c r="P3" s="4" t="n"/>
@@ -819,32 +879,32 @@
       <c r="S3" s="4" t="n"/>
       <c r="T3" s="4" t="n"/>
       <c r="U3" s="4" t="n"/>
-      <c r="V3" s="3" t="inlineStr">
+      <c r="V3" s="4" t="n"/>
+      <c r="W3" s="4" t="n"/>
+      <c r="X3" s="3" t="inlineStr">
         <is>
           <t>ENT-01</t>
         </is>
       </c>
-      <c r="W3" s="3" t="inlineStr">
+      <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>Pipeline Entrance - Sharp Edge</t>
         </is>
       </c>
-      <c r="X3" s="3" t="n">
+      <c r="Z3" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>G1A-5</t>
         </is>
       </c>
-      <c r="Z3" s="3" t="n">
+      <c r="AB3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AA3" s="3" t="n">
+      <c r="AC3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AB3" s="3" t="n"/>
-      <c r="AC3" s="3" t="n"/>
       <c r="AD3" s="3" t="n"/>
       <c r="AE3" s="3" t="n"/>
       <c r="AF3" s="3" t="n"/>
@@ -852,7 +912,17 @@
       <c r="AH3" s="3" t="n"/>
       <c r="AI3" s="3" t="n"/>
       <c r="AJ3" s="3" t="n"/>
-      <c r="AK3" s="3" t="inlineStr">
+      <c r="AK3" s="3" t="n"/>
+      <c r="AL3" s="3" t="n"/>
+      <c r="AM3" s="3" t="n"/>
+      <c r="AN3" s="3" t="n"/>
+      <c r="AO3" s="3" t="n"/>
+      <c r="AP3" s="3" t="n"/>
+      <c r="AQ3" s="3" t="n"/>
+      <c r="AR3" s="3" t="n"/>
+      <c r="AS3" s="3" t="n"/>
+      <c r="AT3" s="3" t="n"/>
+      <c r="AU3" s="3" t="inlineStr">
         <is>
           <t>Entrance</t>
         </is>
@@ -884,8 +954,8 @@
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
-      <c r="L4" s="4" t="n"/>
-      <c r="M4" s="4" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
       <c r="N4" s="4" t="n"/>
       <c r="O4" s="4" t="n"/>
       <c r="P4" s="4" t="n"/>
@@ -894,44 +964,54 @@
       <c r="S4" s="4" t="n"/>
       <c r="T4" s="4" t="n"/>
       <c r="U4" s="4" t="n"/>
-      <c r="V4" s="3" t="inlineStr">
+      <c r="V4" s="4" t="n"/>
+      <c r="W4" s="4" t="n"/>
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>P-001</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>Straight Pipeline</t>
         </is>
       </c>
-      <c r="X4" s="3" t="n">
+      <c r="Z4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>G1A-5</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="n">
+      <c r="AB4" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="AA4" s="3" t="n">
+      <c r="AC4" s="3" t="n">
         <v>-2</v>
       </c>
-      <c r="AB4" s="3" t="inlineStr">
+      <c r="AD4" s="3" t="inlineStr">
         <is>
           <t>DOWN</t>
         </is>
       </c>
-      <c r="AC4" s="3" t="n"/>
-      <c r="AD4" s="3" t="n"/>
       <c r="AE4" s="3" t="n"/>
       <c r="AF4" s="3" t="n"/>
       <c r="AG4" s="3" t="n"/>
       <c r="AH4" s="3" t="n"/>
       <c r="AI4" s="3" t="n"/>
       <c r="AJ4" s="3" t="n"/>
-      <c r="AK4" s="3" t="inlineStr">
+      <c r="AK4" s="3" t="n"/>
+      <c r="AL4" s="3" t="n"/>
+      <c r="AM4" s="3" t="n"/>
+      <c r="AN4" s="3" t="n"/>
+      <c r="AO4" s="3" t="n"/>
+      <c r="AP4" s="3" t="n"/>
+      <c r="AQ4" s="3" t="n"/>
+      <c r="AR4" s="3" t="n"/>
+      <c r="AS4" s="3" t="n"/>
+      <c r="AT4" s="3" t="n"/>
+      <c r="AU4" s="3" t="inlineStr">
         <is>
           <t>Drop leg</t>
         </is>
@@ -963,8 +1043,8 @@
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="n"/>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
       <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="n"/>
       <c r="P5" s="4" t="n"/>
@@ -973,32 +1053,32 @@
       <c r="S5" s="4" t="n"/>
       <c r="T5" s="4" t="n"/>
       <c r="U5" s="4" t="n"/>
-      <c r="V5" s="3" t="inlineStr">
+      <c r="V5" s="4" t="n"/>
+      <c r="W5" s="4" t="n"/>
+      <c r="X5" s="3" t="inlineStr">
         <is>
           <t>EL-001</t>
         </is>
       </c>
-      <c r="W5" s="3" t="inlineStr">
+      <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>Elbow 90 Long</t>
         </is>
       </c>
-      <c r="X5" s="3" t="n">
+      <c r="Z5" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
+      <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>G1A-5</t>
         </is>
       </c>
-      <c r="Z5" s="3" t="n">
+      <c r="AB5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="3" t="n">
+      <c r="AC5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AB5" s="3" t="n"/>
-      <c r="AC5" s="3" t="n"/>
       <c r="AD5" s="3" t="n"/>
       <c r="AE5" s="3" t="n"/>
       <c r="AF5" s="3" t="n"/>
@@ -1007,6 +1087,16 @@
       <c r="AI5" s="3" t="n"/>
       <c r="AJ5" s="3" t="n"/>
       <c r="AK5" s="3" t="n"/>
+      <c r="AL5" s="3" t="n"/>
+      <c r="AM5" s="3" t="n"/>
+      <c r="AN5" s="3" t="n"/>
+      <c r="AO5" s="3" t="n"/>
+      <c r="AP5" s="3" t="n"/>
+      <c r="AQ5" s="3" t="n"/>
+      <c r="AR5" s="3" t="n"/>
+      <c r="AS5" s="3" t="n"/>
+      <c r="AT5" s="3" t="n"/>
+      <c r="AU5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -1031,13 +1121,13 @@
         <v>4</v>
       </c>
       <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n">
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n">
         <v>-0.4</v>
       </c>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
       <c r="N6" s="4" t="n"/>
       <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
@@ -1046,32 +1136,32 @@
       <c r="S6" s="4" t="n"/>
       <c r="T6" s="4" t="n"/>
       <c r="U6" s="4" t="n"/>
-      <c r="V6" s="3" t="inlineStr">
+      <c r="V6" s="4" t="n"/>
+      <c r="W6" s="4" t="n"/>
+      <c r="X6" s="3" t="inlineStr">
         <is>
           <t>TEE-01</t>
         </is>
       </c>
-      <c r="W6" s="3" t="inlineStr">
+      <c r="Y6" s="3" t="inlineStr">
         <is>
           <t>Tee Split Line Flow</t>
         </is>
       </c>
-      <c r="X6" s="3" t="n">
+      <c r="Z6" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
+      <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>G1A-5</t>
         </is>
       </c>
-      <c r="Z6" s="3" t="n">
+      <c r="AB6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AA6" s="3" t="n">
+      <c r="AC6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AB6" s="3" t="n"/>
-      <c r="AC6" s="3" t="n"/>
       <c r="AD6" s="3" t="n"/>
       <c r="AE6" s="3" t="n"/>
       <c r="AF6" s="3" t="n"/>
@@ -1079,7 +1169,17 @@
       <c r="AH6" s="3" t="n"/>
       <c r="AI6" s="3" t="n"/>
       <c r="AJ6" s="3" t="n"/>
-      <c r="AK6" s="3" t="inlineStr">
+      <c r="AK6" s="3" t="n"/>
+      <c r="AL6" s="3" t="n"/>
+      <c r="AM6" s="3" t="n"/>
+      <c r="AN6" s="3" t="n"/>
+      <c r="AO6" s="3" t="n"/>
+      <c r="AP6" s="3" t="n"/>
+      <c r="AQ6" s="3" t="n"/>
+      <c r="AR6" s="3" t="n"/>
+      <c r="AS6" s="3" t="n"/>
+      <c r="AT6" s="3" t="n"/>
+      <c r="AU6" s="3" t="inlineStr">
         <is>
           <t>40% splits to branch</t>
         </is>
@@ -1111,8 +1211,8 @@
       <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="n"/>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="4" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
       <c r="N7" s="4" t="n"/>
       <c r="O7" s="4" t="n"/>
       <c r="P7" s="4" t="n"/>
@@ -1121,42 +1221,52 @@
       <c r="S7" s="4" t="n"/>
       <c r="T7" s="4" t="n"/>
       <c r="U7" s="4" t="n"/>
-      <c r="V7" s="3" t="inlineStr">
+      <c r="V7" s="4" t="n"/>
+      <c r="W7" s="4" t="n"/>
+      <c r="X7" s="3" t="inlineStr">
         <is>
           <t>PSV-01</t>
         </is>
       </c>
-      <c r="W7" s="3" t="inlineStr">
+      <c r="Y7" s="3" t="inlineStr">
         <is>
           <t>Fix Pressure</t>
         </is>
       </c>
-      <c r="X7" s="3" t="n">
+      <c r="Z7" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
+      <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>G1A-5</t>
         </is>
       </c>
-      <c r="Z7" s="3" t="n">
+      <c r="AB7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AA7" s="3" t="n">
+      <c r="AC7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AB7" s="3" t="n"/>
-      <c r="AC7" s="3" t="n"/>
-      <c r="AD7" s="3" t="n">
+      <c r="AD7" s="3" t="n"/>
+      <c r="AE7" s="3" t="n"/>
+      <c r="AF7" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="AE7" s="3" t="n"/>
-      <c r="AF7" s="3" t="n"/>
       <c r="AG7" s="3" t="n"/>
       <c r="AH7" s="3" t="n"/>
       <c r="AI7" s="3" t="n"/>
       <c r="AJ7" s="3" t="n"/>
-      <c r="AK7" s="3" t="inlineStr">
+      <c r="AK7" s="3" t="n"/>
+      <c r="AL7" s="3" t="n"/>
+      <c r="AM7" s="3" t="n"/>
+      <c r="AN7" s="3" t="n"/>
+      <c r="AO7" s="3" t="n"/>
+      <c r="AP7" s="3" t="n"/>
+      <c r="AQ7" s="3" t="n"/>
+      <c r="AR7" s="3" t="n"/>
+      <c r="AS7" s="3" t="n"/>
+      <c r="AT7" s="3" t="n"/>
+      <c r="AU7" s="3" t="inlineStr">
         <is>
           <t>PSV seat loss</t>
         </is>
@@ -1188,8 +1298,8 @@
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="n"/>
-      <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
       <c r="N8" s="4" t="n"/>
       <c r="O8" s="4" t="n"/>
       <c r="P8" s="4" t="n"/>
@@ -1198,32 +1308,32 @@
       <c r="S8" s="4" t="n"/>
       <c r="T8" s="4" t="n"/>
       <c r="U8" s="4" t="n"/>
-      <c r="V8" s="3" t="inlineStr">
+      <c r="V8" s="4" t="n"/>
+      <c r="W8" s="4" t="n"/>
+      <c r="X8" s="3" t="inlineStr">
         <is>
           <t>P-002</t>
         </is>
       </c>
-      <c r="W8" s="3" t="inlineStr">
+      <c r="Y8" s="3" t="inlineStr">
         <is>
           <t>Straight Pipeline</t>
         </is>
       </c>
-      <c r="X8" s="3" t="n">
+      <c r="Z8" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
+      <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>G1A-5</t>
         </is>
       </c>
-      <c r="Z8" s="3" t="n">
+      <c r="AB8" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="AA8" s="3" t="n">
+      <c r="AC8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AB8" s="3" t="n"/>
-      <c r="AC8" s="3" t="n"/>
       <c r="AD8" s="3" t="n"/>
       <c r="AE8" s="3" t="n"/>
       <c r="AF8" s="3" t="n"/>
@@ -1231,7 +1341,17 @@
       <c r="AH8" s="3" t="n"/>
       <c r="AI8" s="3" t="n"/>
       <c r="AJ8" s="3" t="n"/>
-      <c r="AK8" s="3" t="inlineStr">
+      <c r="AK8" s="3" t="n"/>
+      <c r="AL8" s="3" t="n"/>
+      <c r="AM8" s="3" t="n"/>
+      <c r="AN8" s="3" t="n"/>
+      <c r="AO8" s="3" t="n"/>
+      <c r="AP8" s="3" t="n"/>
+      <c r="AQ8" s="3" t="n"/>
+      <c r="AR8" s="3" t="n"/>
+      <c r="AS8" s="3" t="n"/>
+      <c r="AT8" s="3" t="n"/>
+      <c r="AU8" s="3" t="inlineStr">
         <is>
           <t>Header run</t>
         </is>
@@ -1263,8 +1383,8 @@
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="n"/>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
       <c r="N9" s="4" t="n"/>
       <c r="O9" s="4" t="n"/>
       <c r="P9" s="4" t="n"/>
@@ -1273,32 +1393,32 @@
       <c r="S9" s="4" t="n"/>
       <c r="T9" s="4" t="n"/>
       <c r="U9" s="4" t="n"/>
-      <c r="V9" s="3" t="inlineStr">
+      <c r="V9" s="4" t="n"/>
+      <c r="W9" s="4" t="n"/>
+      <c r="X9" s="3" t="inlineStr">
         <is>
           <t>EL-002</t>
         </is>
       </c>
-      <c r="W9" s="3" t="inlineStr">
+      <c r="Y9" s="3" t="inlineStr">
         <is>
           <t>Elbow 90 Long</t>
         </is>
       </c>
-      <c r="X9" s="3" t="n">
+      <c r="Z9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
+      <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>G1A-5</t>
         </is>
       </c>
-      <c r="Z9" s="3" t="n">
+      <c r="AB9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AA9" s="3" t="n">
+      <c r="AC9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AB9" s="3" t="n"/>
-      <c r="AC9" s="3" t="n"/>
       <c r="AD9" s="3" t="n"/>
       <c r="AE9" s="3" t="n"/>
       <c r="AF9" s="3" t="n"/>
@@ -1307,6 +1427,16 @@
       <c r="AI9" s="3" t="n"/>
       <c r="AJ9" s="3" t="n"/>
       <c r="AK9" s="3" t="n"/>
+      <c r="AL9" s="3" t="n"/>
+      <c r="AM9" s="3" t="n"/>
+      <c r="AN9" s="3" t="n"/>
+      <c r="AO9" s="3" t="n"/>
+      <c r="AP9" s="3" t="n"/>
+      <c r="AQ9" s="3" t="n"/>
+      <c r="AR9" s="3" t="n"/>
+      <c r="AS9" s="3" t="n"/>
+      <c r="AT9" s="3" t="n"/>
+      <c r="AU9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1334,8 +1464,8 @@
       <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="n"/>
-      <c r="L10" s="4" t="n"/>
-      <c r="M10" s="4" t="n"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
       <c r="N10" s="4" t="n"/>
       <c r="O10" s="4" t="n"/>
       <c r="P10" s="4" t="n"/>
@@ -1344,42 +1474,52 @@
       <c r="S10" s="4" t="n"/>
       <c r="T10" s="4" t="n"/>
       <c r="U10" s="4" t="n"/>
-      <c r="V10" s="3" t="inlineStr">
+      <c r="V10" s="4" t="n"/>
+      <c r="W10" s="4" t="n"/>
+      <c r="X10" s="3" t="inlineStr">
         <is>
           <t>VLV-01</t>
         </is>
       </c>
-      <c r="W10" s="3" t="inlineStr">
+      <c r="Y10" s="3" t="inlineStr">
         <is>
           <t>Fix K</t>
         </is>
       </c>
-      <c r="X10" s="3" t="n">
+      <c r="Z10" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
+      <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>G1A-5</t>
         </is>
       </c>
-      <c r="Z10" s="3" t="n">
+      <c r="AB10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AA10" s="3" t="n">
+      <c r="AC10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AB10" s="3" t="n"/>
-      <c r="AC10" s="3" t="n">
+      <c r="AD10" s="3" t="n"/>
+      <c r="AE10" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="AD10" s="3" t="n"/>
-      <c r="AE10" s="3" t="n"/>
       <c r="AF10" s="3" t="n"/>
       <c r="AG10" s="3" t="n"/>
       <c r="AH10" s="3" t="n"/>
       <c r="AI10" s="3" t="n"/>
       <c r="AJ10" s="3" t="n"/>
-      <c r="AK10" s="3" t="inlineStr">
+      <c r="AK10" s="3" t="n"/>
+      <c r="AL10" s="3" t="n"/>
+      <c r="AM10" s="3" t="n"/>
+      <c r="AN10" s="3" t="n"/>
+      <c r="AO10" s="3" t="n"/>
+      <c r="AP10" s="3" t="n"/>
+      <c r="AQ10" s="3" t="n"/>
+      <c r="AR10" s="3" t="n"/>
+      <c r="AS10" s="3" t="n"/>
+      <c r="AT10" s="3" t="n"/>
+      <c r="AU10" s="3" t="inlineStr">
         <is>
           <t>CV K=7.2</t>
         </is>
@@ -1413,56 +1553,56 @@
       <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="n"/>
-      <c r="L11" s="4" t="n">
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="4" t="n">
         <v>250</v>
       </c>
-      <c r="M11" s="4" t="n">
+      <c r="O11" s="4" t="n">
         <v>12000</v>
       </c>
-      <c r="N11" s="4" t="n">
+      <c r="P11" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="O11" s="4" t="n">
+      <c r="Q11" s="4" t="n">
         <v>0.012</v>
       </c>
-      <c r="P11" s="4" t="n">
+      <c r="R11" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="Q11" s="4" t="n">
+      <c r="S11" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="R11" s="4" t="n">
+      <c r="T11" s="4" t="n">
         <v>0.45</v>
       </c>
-      <c r="S11" s="4" t="n"/>
-      <c r="T11" s="4" t="n"/>
       <c r="U11" s="4" t="n"/>
-      <c r="V11" s="3" t="inlineStr">
+      <c r="V11" s="4" t="n"/>
+      <c r="W11" s="4" t="n"/>
+      <c r="X11" s="3" t="inlineStr">
         <is>
           <t>P-003</t>
         </is>
       </c>
-      <c r="W11" s="3" t="inlineStr">
+      <c r="Y11" s="3" t="inlineStr">
         <is>
           <t>Straight Pipeline</t>
         </is>
       </c>
-      <c r="X11" s="3" t="n">
+      <c r="Z11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
+      <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>G1A-5</t>
         </is>
       </c>
-      <c r="Z11" s="3" t="n">
+      <c r="AB11" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="AA11" s="3" t="n">
+      <c r="AC11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AB11" s="3" t="n"/>
-      <c r="AC11" s="3" t="n"/>
       <c r="AD11" s="3" t="n"/>
       <c r="AE11" s="3" t="n"/>
       <c r="AF11" s="3" t="n"/>
@@ -1470,7 +1610,17 @@
       <c r="AH11" s="3" t="n"/>
       <c r="AI11" s="3" t="n"/>
       <c r="AJ11" s="3" t="n"/>
-      <c r="AK11" s="3" t="inlineStr">
+      <c r="AK11" s="3" t="n"/>
+      <c r="AL11" s="3" t="n"/>
+      <c r="AM11" s="3" t="n"/>
+      <c r="AN11" s="3" t="n"/>
+      <c r="AO11" s="3" t="n"/>
+      <c r="AP11" s="3" t="n"/>
+      <c r="AQ11" s="3" t="n"/>
+      <c r="AR11" s="3" t="n"/>
+      <c r="AS11" s="3" t="n"/>
+      <c r="AT11" s="3" t="n"/>
+      <c r="AU11" s="3" t="inlineStr">
         <is>
           <t>Manual props (no stream)</t>
         </is>
@@ -1502,8 +1652,8 @@
       <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="n"/>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
       <c r="N12" s="4" t="n"/>
       <c r="O12" s="4" t="n"/>
       <c r="P12" s="4" t="n"/>
@@ -1512,32 +1662,32 @@
       <c r="S12" s="4" t="n"/>
       <c r="T12" s="4" t="n"/>
       <c r="U12" s="4" t="n"/>
-      <c r="V12" s="3" t="inlineStr">
+      <c r="V12" s="4" t="n"/>
+      <c r="W12" s="4" t="n"/>
+      <c r="X12" s="3" t="inlineStr">
         <is>
           <t>EL-003</t>
         </is>
       </c>
-      <c r="W12" s="3" t="inlineStr">
+      <c r="Y12" s="3" t="inlineStr">
         <is>
           <t>Elbow 90 Long</t>
         </is>
       </c>
-      <c r="X12" s="3" t="n">
+      <c r="Z12" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
+      <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>G1A-5</t>
         </is>
       </c>
-      <c r="Z12" s="3" t="n">
+      <c r="AB12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AA12" s="3" t="n">
+      <c r="AC12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AB12" s="3" t="n"/>
-      <c r="AC12" s="3" t="n"/>
       <c r="AD12" s="3" t="n"/>
       <c r="AE12" s="3" t="n"/>
       <c r="AF12" s="3" t="n"/>
@@ -1546,6 +1696,16 @@
       <c r="AI12" s="3" t="n"/>
       <c r="AJ12" s="3" t="n"/>
       <c r="AK12" s="3" t="n"/>
+      <c r="AL12" s="3" t="n"/>
+      <c r="AM12" s="3" t="n"/>
+      <c r="AN12" s="3" t="n"/>
+      <c r="AO12" s="3" t="n"/>
+      <c r="AP12" s="3" t="n"/>
+      <c r="AQ12" s="3" t="n"/>
+      <c r="AR12" s="3" t="n"/>
+      <c r="AS12" s="3" t="n"/>
+      <c r="AT12" s="3" t="n"/>
+      <c r="AU12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1577,8 +1737,8 @@
       <c r="I13" s="3" t="n"/>
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="n"/>
-      <c r="L13" s="4" t="n"/>
-      <c r="M13" s="4" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
       <c r="N13" s="4" t="n"/>
       <c r="O13" s="4" t="n"/>
       <c r="P13" s="4" t="n"/>
@@ -1587,42 +1747,52 @@
       <c r="S13" s="4" t="n"/>
       <c r="T13" s="4" t="n"/>
       <c r="U13" s="4" t="n"/>
-      <c r="V13" s="3" t="inlineStr">
+      <c r="V13" s="4" t="n"/>
+      <c r="W13" s="4" t="n"/>
+      <c r="X13" s="3" t="inlineStr">
         <is>
           <t>SRC-01</t>
         </is>
       </c>
-      <c r="W13" s="3" t="inlineStr">
+      <c r="Y13" s="3" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="X13" s="3" t="n">
+      <c r="Z13" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
+      <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>G1A-5</t>
         </is>
       </c>
-      <c r="Z13" s="3" t="n">
+      <c r="AB13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AA13" s="3" t="n">
+      <c r="AC13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AB13" s="3" t="n"/>
-      <c r="AC13" s="3" t="n"/>
       <c r="AD13" s="3" t="n"/>
       <c r="AE13" s="3" t="n"/>
       <c r="AF13" s="3" t="n"/>
       <c r="AG13" s="3" t="n"/>
-      <c r="AH13" s="3" t="n">
+      <c r="AH13" s="3" t="n"/>
+      <c r="AI13" s="3" t="n"/>
+      <c r="AJ13" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="AI13" s="3" t="n"/>
-      <c r="AJ13" s="3" t="n"/>
-      <c r="AK13" s="3" t="inlineStr">
+      <c r="AK13" s="3" t="n"/>
+      <c r="AL13" s="3" t="n"/>
+      <c r="AM13" s="3" t="n"/>
+      <c r="AN13" s="3" t="n"/>
+      <c r="AO13" s="3" t="n"/>
+      <c r="AP13" s="3" t="n"/>
+      <c r="AQ13" s="3" t="n"/>
+      <c r="AR13" s="3" t="n"/>
+      <c r="AS13" s="3" t="n"/>
+      <c r="AT13" s="3" t="n"/>
+      <c r="AU13" s="3" t="inlineStr">
         <is>
           <t>Upstream source pressure</t>
         </is>
@@ -1654,8 +1824,8 @@
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="n"/>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n"/>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
       <c r="N14" s="4" t="n"/>
       <c r="O14" s="4" t="n"/>
       <c r="P14" s="4" t="n"/>
@@ -1664,32 +1834,32 @@
       <c r="S14" s="4" t="n"/>
       <c r="T14" s="4" t="n"/>
       <c r="U14" s="4" t="n"/>
-      <c r="V14" s="3" t="inlineStr">
+      <c r="V14" s="4" t="n"/>
+      <c r="W14" s="4" t="n"/>
+      <c r="X14" s="3" t="inlineStr">
         <is>
           <t>P-301</t>
         </is>
       </c>
-      <c r="W14" s="3" t="inlineStr">
+      <c r="Y14" s="3" t="inlineStr">
         <is>
           <t>Straight Pipeline</t>
         </is>
       </c>
-      <c r="X14" s="3" t="n">
+      <c r="Z14" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
+      <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>G1A-5</t>
         </is>
       </c>
-      <c r="Z14" s="3" t="n">
+      <c r="AB14" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="AA14" s="3" t="n">
+      <c r="AC14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AB14" s="3" t="n"/>
-      <c r="AC14" s="3" t="n"/>
       <c r="AD14" s="3" t="n"/>
       <c r="AE14" s="3" t="n"/>
       <c r="AF14" s="3" t="n"/>
@@ -1697,7 +1867,17 @@
       <c r="AH14" s="3" t="n"/>
       <c r="AI14" s="3" t="n"/>
       <c r="AJ14" s="3" t="n"/>
-      <c r="AK14" s="3" t="inlineStr">
+      <c r="AK14" s="3" t="n"/>
+      <c r="AL14" s="3" t="n"/>
+      <c r="AM14" s="3" t="n"/>
+      <c r="AN14" s="3" t="n"/>
+      <c r="AO14" s="3" t="n"/>
+      <c r="AP14" s="3" t="n"/>
+      <c r="AQ14" s="3" t="n"/>
+      <c r="AR14" s="3" t="n"/>
+      <c r="AS14" s="3" t="n"/>
+      <c r="AT14" s="3" t="n"/>
+      <c r="AU14" s="3" t="inlineStr">
         <is>
           <t>Run to valve</t>
         </is>
@@ -1729,8 +1909,8 @@
       <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="n"/>
-      <c r="L15" s="4" t="n"/>
-      <c r="M15" s="4" t="n"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
       <c r="N15" s="4" t="n"/>
       <c r="O15" s="4" t="n"/>
       <c r="P15" s="4" t="n"/>
@@ -1739,46 +1919,76 @@
       <c r="S15" s="4" t="n"/>
       <c r="T15" s="4" t="n"/>
       <c r="U15" s="4" t="n"/>
-      <c r="V15" s="3" t="inlineStr">
+      <c r="V15" s="4" t="n"/>
+      <c r="W15" s="4" t="n"/>
+      <c r="X15" s="3" t="inlineStr">
         <is>
           <t>FCV-301</t>
         </is>
       </c>
-      <c r="W15" s="3" t="inlineStr">
+      <c r="Y15" s="3" t="inlineStr">
         <is>
           <t>Control Valve</t>
         </is>
       </c>
-      <c r="X15" s="3" t="n">
+      <c r="Z15" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
+      <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>G1A-5</t>
         </is>
       </c>
-      <c r="Z15" s="3" t="n">
+      <c r="AB15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AA15" s="3" t="n">
+      <c r="AC15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AB15" s="3" t="n"/>
-      <c r="AC15" s="3" t="n"/>
       <c r="AD15" s="3" t="n"/>
       <c r="AE15" s="3" t="n"/>
       <c r="AF15" s="3" t="n"/>
       <c r="AG15" s="3" t="n"/>
       <c r="AH15" s="3" t="n"/>
-      <c r="AI15" s="3" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+      <c r="AI15" s="3" t="n"/>
       <c r="AJ15" s="3" t="n"/>
       <c r="AK15" s="3" t="inlineStr">
         <is>
-          <t>Flow control — ΔP floats to Destination P</t>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AL15" s="3" t="n"/>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Globe</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>Equal%</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP15" s="3" t="n"/>
+      <c r="AQ15" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AR15" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AS15" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Flow control — datasheet auto-sizes Rated Cv (leave Rated Cv blank)</t>
         </is>
       </c>
     </row>
@@ -1808,8 +2018,8 @@
       <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="n"/>
-      <c r="L16" s="4" t="n"/>
-      <c r="M16" s="4" t="n"/>
+      <c r="L16" s="3" t="n"/>
+      <c r="M16" s="3" t="n"/>
       <c r="N16" s="4" t="n"/>
       <c r="O16" s="4" t="n"/>
       <c r="P16" s="4" t="n"/>
@@ -1818,42 +2028,52 @@
       <c r="S16" s="4" t="n"/>
       <c r="T16" s="4" t="n"/>
       <c r="U16" s="4" t="n"/>
-      <c r="V16" s="3" t="inlineStr">
+      <c r="V16" s="4" t="n"/>
+      <c r="W16" s="4" t="n"/>
+      <c r="X16" s="3" t="inlineStr">
         <is>
           <t>DST-01</t>
         </is>
       </c>
-      <c r="W16" s="3" t="inlineStr">
+      <c r="Y16" s="3" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="X16" s="3" t="n">
+      <c r="Z16" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
+      <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>G1A-5</t>
         </is>
       </c>
-      <c r="Z16" s="3" t="n">
+      <c r="AB16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AA16" s="3" t="n">
+      <c r="AC16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AB16" s="3" t="n"/>
-      <c r="AC16" s="3" t="n"/>
       <c r="AD16" s="3" t="n"/>
       <c r="AE16" s="3" t="n"/>
       <c r="AF16" s="3" t="n"/>
       <c r="AG16" s="3" t="n"/>
-      <c r="AH16" s="3" t="n">
+      <c r="AH16" s="3" t="n"/>
+      <c r="AI16" s="3" t="n"/>
+      <c r="AJ16" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="AI16" s="3" t="n"/>
-      <c r="AJ16" s="3" t="n"/>
-      <c r="AK16" s="3" t="inlineStr">
+      <c r="AK16" s="3" t="n"/>
+      <c r="AL16" s="3" t="n"/>
+      <c r="AM16" s="3" t="n"/>
+      <c r="AN16" s="3" t="n"/>
+      <c r="AO16" s="3" t="n"/>
+      <c r="AP16" s="3" t="n"/>
+      <c r="AQ16" s="3" t="n"/>
+      <c r="AR16" s="3" t="n"/>
+      <c r="AS16" s="3" t="n"/>
+      <c r="AT16" s="3" t="n"/>
+      <c r="AU16" s="3" t="inlineStr">
         <is>
           <t>Downstream destination pressure</t>
         </is>
@@ -1889,8 +2109,8 @@
       <c r="I17" s="3" t="n"/>
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="n"/>
-      <c r="L17" s="4" t="n"/>
-      <c r="M17" s="4" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
       <c r="N17" s="4" t="n"/>
       <c r="O17" s="4" t="n"/>
       <c r="P17" s="4" t="n"/>
@@ -1899,42 +2119,52 @@
       <c r="S17" s="4" t="n"/>
       <c r="T17" s="4" t="n"/>
       <c r="U17" s="4" t="n"/>
-      <c r="V17" s="3" t="inlineStr">
+      <c r="V17" s="4" t="n"/>
+      <c r="W17" s="4" t="n"/>
+      <c r="X17" s="3" t="inlineStr">
         <is>
           <t>SRC-02</t>
         </is>
       </c>
-      <c r="W17" s="3" t="inlineStr">
+      <c r="Y17" s="3" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="X17" s="3" t="n">
+      <c r="Z17" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
+      <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>G1A-5</t>
         </is>
       </c>
-      <c r="Z17" s="3" t="n">
+      <c r="AB17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AA17" s="3" t="n">
+      <c r="AC17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AB17" s="3" t="n"/>
-      <c r="AC17" s="3" t="n"/>
       <c r="AD17" s="3" t="n"/>
       <c r="AE17" s="3" t="n"/>
       <c r="AF17" s="3" t="n"/>
       <c r="AG17" s="3" t="n"/>
-      <c r="AH17" s="3" t="n">
+      <c r="AH17" s="3" t="n"/>
+      <c r="AI17" s="3" t="n"/>
+      <c r="AJ17" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="AI17" s="3" t="n"/>
-      <c r="AJ17" s="3" t="n"/>
-      <c r="AK17" s="3" t="inlineStr">
+      <c r="AK17" s="3" t="n"/>
+      <c r="AL17" s="3" t="n"/>
+      <c r="AM17" s="3" t="n"/>
+      <c r="AN17" s="3" t="n"/>
+      <c r="AO17" s="3" t="n"/>
+      <c r="AP17" s="3" t="n"/>
+      <c r="AQ17" s="3" t="n"/>
+      <c r="AR17" s="3" t="n"/>
+      <c r="AS17" s="3" t="n"/>
+      <c r="AT17" s="3" t="n"/>
+      <c r="AU17" s="3" t="inlineStr">
         <is>
           <t>Header source</t>
         </is>
@@ -1963,13 +2193,13 @@
         <v>2</v>
       </c>
       <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n">
+      <c r="I18" s="3" t="n"/>
+      <c r="J18" s="3" t="n"/>
+      <c r="K18" s="3" t="n">
         <v>-0.5</v>
       </c>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="n"/>
-      <c r="L18" s="4" t="n"/>
-      <c r="M18" s="4" t="n"/>
+      <c r="L18" s="3" t="n"/>
+      <c r="M18" s="3" t="n"/>
       <c r="N18" s="4" t="n"/>
       <c r="O18" s="4" t="n"/>
       <c r="P18" s="4" t="n"/>
@@ -1978,32 +2208,32 @@
       <c r="S18" s="4" t="n"/>
       <c r="T18" s="4" t="n"/>
       <c r="U18" s="4" t="n"/>
-      <c r="V18" s="3" t="inlineStr">
+      <c r="V18" s="4" t="n"/>
+      <c r="W18" s="4" t="n"/>
+      <c r="X18" s="3" t="inlineStr">
         <is>
           <t>TEE-40</t>
         </is>
       </c>
-      <c r="W18" s="3" t="inlineStr">
+      <c r="Y18" s="3" t="inlineStr">
         <is>
           <t>Tee Split Branch Flow 1</t>
         </is>
       </c>
-      <c r="X18" s="3" t="n">
+      <c r="Z18" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
+      <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>G1A-5</t>
         </is>
       </c>
-      <c r="Z18" s="3" t="n">
+      <c r="AB18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AA18" s="3" t="n">
+      <c r="AC18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AB18" s="3" t="n"/>
-      <c r="AC18" s="3" t="n"/>
       <c r="AD18" s="3" t="n"/>
       <c r="AE18" s="3" t="n"/>
       <c r="AF18" s="3" t="n"/>
@@ -2011,7 +2241,17 @@
       <c r="AH18" s="3" t="n"/>
       <c r="AI18" s="3" t="n"/>
       <c r="AJ18" s="3" t="n"/>
-      <c r="AK18" s="3" t="inlineStr">
+      <c r="AK18" s="3" t="n"/>
+      <c r="AL18" s="3" t="n"/>
+      <c r="AM18" s="3" t="n"/>
+      <c r="AN18" s="3" t="n"/>
+      <c r="AO18" s="3" t="n"/>
+      <c r="AP18" s="3" t="n"/>
+      <c r="AQ18" s="3" t="n"/>
+      <c r="AR18" s="3" t="n"/>
+      <c r="AS18" s="3" t="n"/>
+      <c r="AT18" s="3" t="n"/>
+      <c r="AU18" s="3" t="inlineStr">
         <is>
           <t>50% splits to parallel branch</t>
         </is>
@@ -2043,8 +2283,8 @@
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="n"/>
-      <c r="L19" s="4" t="n"/>
-      <c r="M19" s="4" t="n"/>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" s="3" t="n"/>
       <c r="N19" s="4" t="n"/>
       <c r="O19" s="4" t="n"/>
       <c r="P19" s="4" t="n"/>
@@ -2053,48 +2293,68 @@
       <c r="S19" s="4" t="n"/>
       <c r="T19" s="4" t="n"/>
       <c r="U19" s="4" t="n"/>
-      <c r="V19" s="3" t="inlineStr">
+      <c r="V19" s="4" t="n"/>
+      <c r="W19" s="4" t="n"/>
+      <c r="X19" s="3" t="inlineStr">
         <is>
           <t>FCV-40A</t>
         </is>
       </c>
-      <c r="W19" s="3" t="inlineStr">
+      <c r="Y19" s="3" t="inlineStr">
         <is>
           <t>Control Valve</t>
         </is>
       </c>
-      <c r="X19" s="3" t="n">
+      <c r="Z19" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
+      <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>G1A-5</t>
         </is>
       </c>
-      <c r="Z19" s="3" t="n">
+      <c r="AB19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AA19" s="3" t="n">
+      <c r="AC19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AB19" s="3" t="n"/>
-      <c r="AC19" s="3" t="n"/>
-      <c r="AD19" s="3" t="n">
+      <c r="AD19" s="3" t="n"/>
+      <c r="AE19" s="3" t="n"/>
+      <c r="AF19" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="AE19" s="3" t="n"/>
-      <c r="AF19" s="3" t="n"/>
       <c r="AG19" s="3" t="n"/>
       <c r="AH19" s="3" t="n"/>
-      <c r="AI19" s="3" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+      <c r="AI19" s="3" t="n"/>
       <c r="AJ19" s="3" t="n"/>
       <c r="AK19" s="3" t="inlineStr">
         <is>
-          <t>Main-leg valve (50% flow)</t>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AL19" s="3" t="n"/>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Globe</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>Equal%</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="n"/>
+      <c r="AP19" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AQ19" s="3" t="n"/>
+      <c r="AR19" s="3" t="n"/>
+      <c r="AS19" s="3" t="n"/>
+      <c r="AT19" s="3" t="n"/>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Existing valve — Rated Cv 50 given → adequacy check</t>
         </is>
       </c>
     </row>
@@ -2126,8 +2386,8 @@
       <c r="I20" s="3" t="n"/>
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="n"/>
-      <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n"/>
+      <c r="L20" s="3" t="n"/>
+      <c r="M20" s="3" t="n"/>
       <c r="N20" s="4" t="n"/>
       <c r="O20" s="4" t="n"/>
       <c r="P20" s="4" t="n"/>
@@ -2136,65 +2396,84 @@
       <c r="S20" s="4" t="n"/>
       <c r="T20" s="4" t="n"/>
       <c r="U20" s="4" t="n"/>
-      <c r="V20" s="3" t="inlineStr">
+      <c r="V20" s="4" t="n"/>
+      <c r="W20" s="4" t="n"/>
+      <c r="X20" s="3" t="inlineStr">
         <is>
           <t>FCV-40B</t>
         </is>
       </c>
-      <c r="W20" s="3" t="inlineStr">
+      <c r="Y20" s="3" t="inlineStr">
         <is>
           <t>Control Valve</t>
         </is>
       </c>
-      <c r="X20" s="3" t="n">
+      <c r="Z20" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
+      <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>G1A-5</t>
         </is>
       </c>
-      <c r="Z20" s="3" t="n">
+      <c r="AB20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AA20" s="3" t="n">
+      <c r="AC20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AB20" s="3" t="n"/>
-      <c r="AC20" s="3" t="n"/>
-      <c r="AD20" s="3" t="n">
+      <c r="AD20" s="3" t="n"/>
+      <c r="AE20" s="3" t="n"/>
+      <c r="AF20" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="AE20" s="3" t="n"/>
-      <c r="AF20" s="3" t="n"/>
       <c r="AG20" s="3" t="n"/>
       <c r="AH20" s="3" t="n"/>
-      <c r="AI20" s="3" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+      <c r="AI20" s="3" t="n"/>
       <c r="AJ20" s="3" t="n"/>
       <c r="AK20" s="3" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AL20" s="3" t="n"/>
+      <c r="AM20" s="3" t="n"/>
+      <c r="AN20" s="3" t="n"/>
+      <c r="AO20" s="3" t="n"/>
+      <c r="AP20" s="3" t="n"/>
+      <c r="AQ20" s="3" t="n"/>
+      <c r="AR20" s="3" t="n"/>
+      <c r="AS20" s="3" t="n"/>
+      <c r="AT20" s="3" t="n"/>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
           <t>Parallel-leg valve (other 50% flow)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AK2"/>
+  <autoFilter ref="A2:AU2"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:AK1"/>
+    <mergeCell ref="A1:AU1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="6">
     <dataValidation sqref="F3:F2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Main,Branch"</formula1>
     </dataValidation>
-    <dataValidation sqref="AI3:AI2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Control Valve Type" error="F=flow, P=pressure, T=temperature, L=level control" type="list">
+    <dataValidation sqref="AK3:AK2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Control Valve Type" error="F=flow, P=pressure, T=temperature, L=level control" type="list">
       <formula1>"F,P,T,L"</formula1>
     </dataValidation>
-    <dataValidation sqref="W3:W2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Fitting" error="Choose a fitting from the list" type="list">
-      <formula1>_FittingList!$A$1:$A$58</formula1>
+    <dataValidation sqref="AM3:AM2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valve Body Style" error="Valve body style" type="list">
+      <formula1>"Globe,Angle,Ball,Butterfly,Eccentric"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AN3:AN2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valve Characteristic" error="Inherent trim characteristic (F &amp; L valves)" type="list">
+      <formula1>"Linear,Equal%,Quick-Open"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AT3:AT2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Seat Leakage Class" error="FCI 70-2 / IEC 60534-4 seat leakage class" type="list">
+      <formula1>"II,III,IV,V,VI"</formula1>
+    </dataValidation>
+    <dataValidation sqref="Y3:Y2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Fitting" error="Choose a fitting from the list" type="list">
+      <formula1>_FittingList!$A$1:$A$66</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2207,7 +2486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A58"/>
+  <dimension ref="A1:A66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2528,89 +2807,145 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Tee Join Line Flow</t>
+          <t>Tee Join Branch Flow 3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tee Split Branch Flow 1</t>
+          <t>Tee Join Branch Flow 4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Tee Split Branch Flow 2</t>
+          <t>Tee Join Branch Flow 5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Tee Split Line Flow</t>
+          <t>Tee Join Branch Flow 6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Fix Pressure</t>
+          <t>Tee Join Line Flow</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Fix K</t>
+          <t>Tee Split Branch Flow 1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Nozzle</t>
+          <t>Tee Split Branch Flow 2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Orifice</t>
+          <t>Tee Split Branch Flow 3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Straight Pipeline</t>
+          <t>Tee Split Branch Flow 4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Venturi</t>
+          <t>Tee Split Branch Flow 5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Tee Split Branch Flow 6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Control Valve</t>
+          <t>Tee Split Line Flow</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
+        <is>
+          <t>Fix Pressure</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Fix K</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Nozzle</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Orifice</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Straight Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Venturi</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Control Valve</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
@@ -2627,7 +2962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A64"/>
+  <dimension ref="A1:A102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -2741,98 +3076,106 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr"/>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERRIDE MODE: with Stream Lookup filled (pulling an HMB stream), filling a yellow cell on</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>FLOW FRACTION FROM MAIN (Tee split / merge)</t>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ANY row of that stream makes the typed value win over the HMB property for that field —</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  On a Tee fitting row, enter a SIGNED fraction of the Main flow:</t>
+          <t xml:space="preserve">  e.g. type a Vapor Mass Flow to test a different rate without touching the HMB file.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    negative  = SPLIT  (that fraction leaves the line)</t>
+          <t xml:space="preserve">  The override persists on every row downstream until changed again or a new stream loads.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    positive  = MERGE  (that fraction joins the line)</t>
-        </is>
-      </c>
+      <c r="A22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  The running vapour &amp; liquid mass flows are scaled in Seq order; downstream dP follows.</t>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>FLOW FRACTION FROM MAIN (Tee split / merge)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr"/>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  On a Tee fitting row, enter a SIGNED fraction of the Main flow:</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>MULTIPLE LINES IN SERIES</t>
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    negative  = SPLIT   (that fraction of the CURRENT flow leaves the line)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Change Line No to mark a new pipe line.  Keep Circuit the same.</t>
+          <t xml:space="preserve">    positive  = MERGE   (running flow becomes that fraction of the ORIGINAL Main flow —</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  The outlet pressure of the last component of Line N becomes the inlet pressure of Line N+1.</t>
+          <t xml:space="preserve">                         an absolute target, e.g. 0.125 → 0.25 → 0.5 → 1.0 builds a header</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr"/>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                         up in stages as branches join it)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>FITTINGS</t>
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  The running vapour &amp; liquid mass flows are scaled in Seq order; downstream dP follows.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Select from the Fitting Name drop-down.  K values applied automatically.</t>
-        </is>
-      </c>
+      <c r="A30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr"/>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>MULTIPLE LINES IN SERIES</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>FIX K  (Fitting = 'Fix K')</t>
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Change Line No to mark a new pipe line.  Keep Circuit the same.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Enter K in the Fixed K column.  Darcy-Weisbach friction and elevation terms still apply.</t>
+          <t xml:space="preserve">  The outlet pressure of the last component of Line N becomes the inlet pressure of Line N+1.</t>
         </is>
       </c>
     </row>
@@ -2842,14 +3185,14 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>FIX PRESSURE  (Fitting = 'Fix Pressure')</t>
+          <t>FITTINGS</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Enter dP (psi) in Fixed dP.  All hydraulics skipped; dP subtracted directly.</t>
+          <t xml:space="preserve">  Select from the Fitting Name drop-down.  K values applied automatically.</t>
         </is>
       </c>
     </row>
@@ -2859,14 +3202,14 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>FLOW ORIFICE  (Instr Type = FO)</t>
+          <t>FIX K  (Fitting = 'Fix K')</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Set Instr Type = FO.  Enter rated dP in Instr dP (psi).</t>
+          <t xml:space="preserve">  Enter K in the Fixed K column.  Darcy-Weisbach friction and elevation terms still apply.</t>
         </is>
       </c>
     </row>
@@ -2876,35 +3219,31 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>SOURCE / DESTINATION  (boundary fittings)</t>
+          <t>FIX PRESSURE  (Fitting = 'Fix Pressure')</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Source: enter the upstream pressure in 'Set P (psia)' — it anchors the circuit inlet pressure.</t>
+          <t xml:space="preserve">  Enter dP (psi) in Fixed dP.  All hydraulics skipped; dP subtracted directly.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Destination: enter the downstream pressure in 'Set P (psia)' — the target the circuit must reach.</t>
-        </is>
-      </c>
+      <c r="A43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  If BOTH are filled, a Control Valve placed between them absorbs the pressure difference.</t>
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>FLOW ORIFICE  (Instr Type = FO)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  If only one is filled, the pressure is taken from that single value.</t>
+          <t xml:space="preserve">  Set Instr Type = FO.  Enter rated dP in Instr dP (psi).</t>
         </is>
       </c>
     </row>
@@ -2914,116 +3253,370 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>CONTROL VALVE  (Fitting = 'Control Valve')</t>
+          <t>SOURCE / DESTINATION  (boundary fittings)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Set 'Control Valve Type' = F (flow), P (pressure), T (temperature) or L (level).</t>
+          <t xml:space="preserve">  Source: enter the upstream pressure in 'Set P (psia)' — it anchors the circuit inlet pressure.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  F (flow): ΔP floats so the running pressure lands on the downstream Destination 'Set P'.</t>
+          <t xml:space="preserve">  Destination: enter the downstream pressure in 'Set P (psia)' — the target the circuit must reach.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  P / L: fixed design ΔP — enter it in 'Fixed dP (psi)' (or a resistance in 'Fixed K').</t>
+          <t xml:space="preserve">  If BOTH are filled, a Control Valve placed between them absorbs the pressure difference.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  T (temperature): like a fixed ΔP, but floored at 'Exch Max Allow dP (psi)' (exchanger limit).</t>
+          <t xml:space="preserve">  If only one is filled, the pressure is taken from that single value.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  β ratio = valve Bore (in) ÷ upstream line bore is reported in the Notes column.</t>
-        </is>
-      </c>
+      <c r="A52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  SERIES valves: place several Control Valve rows in Seq order on the same run.</t>
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>CONTROL VALVE  (Fitting = 'Control Valve')</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PARALLEL valves: split flow at a Tee (negative 'Flow Fraction from Main'), put one Control</t>
+          <t xml:space="preserve">  Set 'Control Valve Type' = F (flow), P (pressure), T (temperature) or L (level).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Valve on the Main leg and one on a Branch (Run Type = Branch, with its own Start P).</t>
+          <t xml:space="preserve">  F (flow): ΔP floats so the running pressure lands on the downstream Destination 'Set P'.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr"/>
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  P / L: fixed design ΔP — enter it in 'Fixed dP (psi)' (or a resistance in 'Fixed K').</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>BRANCHES</t>
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  T (temperature): like a fixed ΔP, but floored at 'Exch Max Allow dP (psi)' (exchanger limit).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Set Run Type = Branch.  Fill Start P on the first Branch row.</t>
+          <t xml:space="preserve">  P &amp; T both honour 'Exch Max Allow dP (psi)' as a MINIMUM ΔP floor across the valve.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Branches are marched independently.  FIV/AIV/regime sheets use the Main run.</t>
+          <t xml:space="preserve">  β ratio = valve Bore (in) ÷ upstream line bore is reported in the Notes column.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr"/>
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SERIES valves: place several Control Valve rows in Seq order on the same run.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>UNITS</t>
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PARALLEL valves: split flow at a Tee (negative 'Flow Fraction from Main'), put one Control</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">    Valve on the Main leg and one on a Branch (Run Type = Branch, with its own Start P).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>CONTROL VALVE DATASHEET  (one sheet per Control Valve, IEC 60534)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Each Control Valve row produces a 'CV_&lt;tag&gt;' datasheet: Min/Norm/Max sizing, cavitation,</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  seat leakage, β ratio and IEC 60534-8-3/-8-4 dB(A) noise vs the limit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Valve Body Style : Globe / Angle / Ball / Butterfly / Eccentric (sets typical FL/xT/Fd).</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Valve Characteristic : Linear / Equal% / Quick-Open (F &amp; L valves) — drives % travel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Rated Cv : enter the EXISTING valve's Cv100 → ADEQUACY CHECK mode (verifies that valve).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             Leave BLANK → SIZING/SELECTION mode (engine picks a generic Rated Cv so the</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             required Cv, travel window and dB(A) limit are met where physically possible).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Design Opening % : target max-flow % travel used when the engine auto-selects Rated Cv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Min/Max Flow Mult : turndown multiples of the marched Normal flow (defaults 0.35 / 1.20).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Noise Limit dBA : project sound limit (default 85).  Exceedance is flagged + mitigations</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             recommended (Rated-Cv choice cannot change service ΔP/noise — use low-noise /</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             multistage trim, a larger body, or split the ΔP across two valves).</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Seat Leakage Class : II/III/IV/V/VI (FCI 70-2 / IEC 60534-4); default IV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>BRANCHES</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Set Run Type = Branch.  Fill Start P on the first Branch row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Branches are marched independently.  FIV/AIV/regime sheets use the Main run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>AUTO-LINKED SPLITS &amp; JOINS (Main ↔ Branch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  JOIN (Branch → Main): on a Main row, set Fitting = 'Tee Join Branch Flow N'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  The Nth Branch block sharing that row's Line No is auto-matched by ordinal count;</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  its real flashed outlet (flow + composition) is blended into Main at that row — no</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  manual entry needed on the Branch side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SPLIT (Main → Branch): on a Main row, set Fitting = 'Tee Split Branch Flow N' with a</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  negative 'Flow Fraction from Main'.  The exact flow + composition that leaves Main at</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  that row is captured and auto-fed as the Branch's inlet — the Branch needs no Stream</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Lookup or manual properties of its own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Upstream Line No (Branch, optional): which Main Line No this Branch splits from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Blank → defaults to the most recently seen Main Line No.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Upstream Seq (Branch, optional): the exact Seq of the Main 'Tee Split Branch Flow N' row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Blank → matched by ordinal count, same as the Join side (N = 1, 2, 3 … up to 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A Branch with no Upstream Line No match falls back to standalone marching (own Stream</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Lookup / manual properties / circuit default).</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>UNITS</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">  This workbook is in FPS units (see the UNITS sheet).</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  Change the Unit System cell (or per-quantity overrides) on the UNITS sheet and enter values accordingly —</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  the engine reads the UNITS sheet and presents all results in the same units.  Bore/NPS is ALWAYS inches.</t>
         </is>
